--- a/resources/tools/grant-reporting-process-map.xlsx
+++ b/resources/tools/grant-reporting-process-map.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="8_{A2BAA402-FE48-40E1-844F-CD57BBDC4657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7927327-09FC-47AE-BF91-5147ECF75FB7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{2075FB50-EC25-400D-9616-EA3117EF0744}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="0" xr2:uid="{2075FB50-EC25-400D-9616-EA3117EF0744}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="2" r:id="rId1"/>
